--- a/wfos_ics/config-files/wfos-rgriphcd/RGRIP_Lookup_Table_Angles.xlsx
+++ b/wfos_ics/config-files/wfos-rgriphcd/RGRIP_Lookup_Table_Angles.xlsx
@@ -762,7 +762,7 @@
         <v>35</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL2" s="1" t="s">
         <v>37</v>
